--- a/04_DESIGN_TABLES/DesignTable_5404N_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5404N_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,11 +697,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5404-N-4-4 X 2</t>
+          <t>5404-N-04X2.500</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="n">
         <v>0.28</v>
@@ -755,23 +755,23 @@
         <v>0.21647</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
         <v>0.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
         <v>0.3</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>5404-N-4-4 X 2</t>
+          <t>5404-N-04X2.500</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -801,23 +801,28 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Air-Way s84 only (double-pass 14 rows); PN carries cut length; C = body OD (no hex) | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5404-N-04X2.000</t>
+          <t>5404-N-04X2.500</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5404-N-4-4 X 3</t>
+          <t>5404-N-04X3.500</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C4" t="n">
         <v>0.28</v>
@@ -871,23 +876,23 @@
         <v>0.21647</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
         <v>0.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W4" t="n">
         <v>0.3</v>
       </c>
       <c r="X4" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>5404-N-4-4 X 3</t>
+          <t>5404-N-04X3.500</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -917,126 +922,2783 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Air-Way s84 only (double-pass 14 rows); PN carries cut length; C = body OD (no hex) | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5404-N-04X3.000</t>
+          <t>5404-N-04X3.500</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5404-N-8-8 X 4</t>
+          <t>5404-N-04X4.000</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="D5" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="F5" t="n">
         <v>1.7899</v>
       </c>
       <c r="G5" t="n">
-        <v>0.81557</v>
+        <v>0.52183</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="J5" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="K5" t="n">
-        <v>0.35064</v>
+        <v>0.21647</v>
       </c>
       <c r="L5" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="N5" t="n">
         <v>1.7899</v>
       </c>
       <c r="O5" t="n">
-        <v>0.81557</v>
+        <v>0.52183</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5337</v>
+        <v>0.4018</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="R5" t="n">
-        <v>0.40779</v>
+        <v>0.26092</v>
       </c>
       <c r="S5" t="n">
-        <v>0.35064</v>
+        <v>0.21647</v>
       </c>
       <c r="T5" t="n">
         <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="X5" t="n">
         <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>5404-N-04X4.000</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/4-18 NPTF x 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>5404-N-04X4.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5404-N-04X4.500</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>5404-N-04X4.500</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/4-18 NPTF x 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>5404-N-04X4.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>5404-N-04X5.000</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>5404-N-04X5.000</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/4-18 NPTF x 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>5404-N-04X5.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5404-N-04X5.500</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>5404-N-04X5.500</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/4-18 NPTF x 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>5404-N-04X5.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5404-N-04X6.000</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>5404-N-04X6.000</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/4-18 NPTF x 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>5404-N-04X6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5404-N-06X2.000</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>5404-N-06X2.000</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 3/8-18 NPTF x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION); round bar only 0.0040 (radius) above the NPTFM crest cone at the end of the thread: modelled as that small step, as at every 5404N size - the vanish threads of the real part (crest cone running on into the bar) are NOT modelled (ASSUMPTION); allowed because the step is at least 0.0025 = half the 0.01 print step of Air-Way C, so the bar stays above the crest cone even if the true C is 0.005 smaller; End A: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic; End B: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39 | ROUND-BAR STEP End A: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005); ROUND-BAR STEP End B: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005)</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>5404-N-06X2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5404-N-06X2.500</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>5404-N-06X2.500</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 3/8-18 NPTF x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION); round bar only 0.0040 (radius) above the NPTFM crest cone at the end of the thread: modelled as that small step, as at every 5404N size - the vanish threads of the real part (crest cone running on into the bar) are NOT modelled (ASSUMPTION); allowed because the step is at least 0.0025 = half the 0.01 print step of Air-Way C, so the bar stays above the crest cone even if the true C is 0.005 smaller; End A: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic; End B: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39 | ROUND-BAR STEP End A: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005); ROUND-BAR STEP End B: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005)</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>5404-N-06X2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5404-N-06X3.000</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>5404-N-06X3.000</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 3/8-18 NPTF x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION); round bar only 0.0040 (radius) above the NPTFM crest cone at the end of the thread: modelled as that small step, as at every 5404N size - the vanish threads of the real part (crest cone running on into the bar) are NOT modelled (ASSUMPTION); allowed because the step is at least 0.0025 = half the 0.01 print step of Air-Way C, so the bar stays above the crest cone even if the true C is 0.005 smaller; End A: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic; End B: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39 | ROUND-BAR STEP End A: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005); ROUND-BAR STEP End B: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005)</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>5404-N-06X3.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5404-N-06X3.500</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>5404-N-06X3.500</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 3/8-18 NPTF x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION); round bar only 0.0040 (radius) above the NPTFM crest cone at the end of the thread: modelled as that small step, as at every 5404N size - the vanish threads of the real part (crest cone running on into the bar) are NOT modelled (ASSUMPTION); allowed because the step is at least 0.0025 = half the 0.01 print step of Air-Way C, so the bar stays above the crest cone even if the true C is 0.005 smaller; End A: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic; End B: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan catalog row misprinted: A1 / A2 DRILL = 3.500 / 88.90 (the length in inch and mm; verify/png/TFA_p12_L3.png) | ROUND-BAR STEP End A: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005); ROUND-BAR STEP End B: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005)</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>5404-N-06X3.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5404-N-06X4.000</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>5404-N-06X4.000</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 3/8-18 NPTF x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION); round bar only 0.0040 (radius) above the NPTFM crest cone at the end of the thread: modelled as that small step, as at every 5404N size - the vanish threads of the real part (crest cone running on into the bar) are NOT modelled (ASSUMPTION); allowed because the step is at least 0.0025 = half the 0.01 print step of Air-Way C, so the bar stays above the crest cone even if the true C is 0.005 smaller; End A: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic; End B: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39 | ROUND-BAR STEP End A: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005); ROUND-BAR STEP End B: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005)</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>5404-N-06X4.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5404-N-06X4.500</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>5404-N-06X4.500</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 3/8-18 NPTF x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION); round bar only 0.0040 (radius) above the NPTFM crest cone at the end of the thread: modelled as that small step, as at every 5404N size - the vanish threads of the real part (crest cone running on into the bar) are NOT modelled (ASSUMPTION); allowed because the step is at least 0.0025 = half the 0.01 print step of Air-Way C, so the bar stays above the crest cone even if the true C is 0.005 smaller; End A: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic; End B: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-21 (batch 20): L from the part number, bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18), as every 06 sibling row; MISSING -&gt; ASSUMED | ROUND-BAR STEP End A: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005); ROUND-BAR STEP End B: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005)</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>5404-N-06X4.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>5404-N-06X5.000</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>5404-N-06X5.000</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 3/8-18 NPTF x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION); round bar only 0.0040 (radius) above the NPTFM crest cone at the end of the thread: modelled as that small step, as at every 5404N size - the vanish threads of the real part (crest cone running on into the bar) are NOT modelled (ASSUMPTION); allowed because the step is at least 0.0025 = half the 0.01 print step of Air-Way C, so the bar stays above the crest cone even if the true C is 0.005 smaller; End A: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic; End B: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39 | ROUND-BAR STEP End A: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005); ROUND-BAR STEP End B: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005)</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>5404-N-06X5.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5404-N-06X5.500</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>5404-N-06X5.500</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 3/8-18 NPTF x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; L from the part number (= Brennan TFA p.11); bar dia / bores from the Air-Way nipple 5404-N-06-06-X1 (A4 transfer); NPTF ends ASME | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION); round bar only 0.0040 (radius) above the NPTFM crest cone at the end of the thread: modelled as that small step, as at every 5404N size - the vanish threads of the real part (crest cone running on into the bar) are NOT modelled (ASSUMPTION); allowed because the step is at least 0.0025 = half the 0.01 print step of Air-Way C, so the bar stays above the crest cone even if the true C is 0.005 smaller; End A: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic; End B: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; L from the part number, bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); no Brennan size used | 2026-10-21 (batch 20): L from the part number, bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18), as every 06 sibling row; MISSING -&gt; ASSUMED | ROUND-BAR STEP End A: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005); ROUND-BAR STEP End B: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005)</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>5404-N-06X5.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5404-N-06X6.000</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>5404-N-06X6.000</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 3/8-18 NPTF x 3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION); round bar only 0.0040 (radius) above the NPTFM crest cone at the end of the thread: modelled as that small step, as at every 5404N size - the vanish threads of the real part (crest cone running on into the bar) are NOT modelled (ASSUMPTION); allowed because the step is at least 0.0025 = half the 0.01 print step of Air-Way C, so the bar stays above the crest cone even if the true C is 0.005 smaller; End A: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic; End B: helical thread stops 0.005 short of the round-bar shoulder (helix 0.4028 vs thread length 0.4078): at the full length the swept tooth ends on the shoulder edge and SolidWorks cannot cut it (QA #178) - threads are cosmetic</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39 | ROUND-BAR STEP End A: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005); ROUND-BAR STEP End B: bar dia 0.6900 (Air-Way C) is only 0.0040 (radius) above the NPTFM end at 0.4078 from its tip (dia 0.6819 = ASME B1.20.3 crest cone E0 + 0.8P + L2/16) - built with that step (round bar: allowed down to 0.0025, half the 0.01 print step of C; a hex body needs 0.005)</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>5404-N-06X6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5404-N-08X2.500</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>5404-N-08X2.500</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/2-14 NPTF x 1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-21 (batch 20): L from the part number, bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18), as every 08 sibling row; MISSING -&gt; ASSUMED</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>5404-N-08X2.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5404-N-08X3.500</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>5404-N-08X3.500</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/2-14 NPTF x 1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18); Brennan prints a different through drill 0.531 (A1 / A2 DRILL) vs the Air-Way transfer 0.48</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>5404-N-08X3.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5404-N-08X4.500</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>5404-N-08X4.500</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/2-14 NPTF x 1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18); Brennan prints a different through drill 0.531 (A1 / A2 DRILL) vs the Air-Way transfer 0.48</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>5404-N-08X4.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>5404-N-08X5.000</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>5404-N-08X5.000</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/2-14 NPTF x 1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18); Brennan prints a different through drill 0.531 (A1 / A2 DRILL) vs the Air-Way transfer 0.48</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>5404-N-08X5.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5404-N-08X5.500</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>5404-N-08X5.500</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/2-14 NPTF x 1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-21 (batch 20): L from the part number, bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18), as every 08 sibling row; MISSING -&gt; ASSUMED</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>5404-N-08X5.500</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>5404-N-08X6.000</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V24" t="n">
+        <v>3</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>5404-N-08X6.000</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/2-14 NPTF x 1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18); Brennan prints a different through drill 0.531 (A1 / A2 DRILL) vs the Air-Way transfer 0.48</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>5404-N-08X6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>5404-N-4-4 X 2</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>5404-N-4-4 X 2</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/4-18 NPTF x 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Air-Way s84 only (double-pass 14 rows); PN carries cut length; C = body OD (no hex) | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>5404-N-04X2.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5404-N-4-4 X 3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>5404-N-4-4 X 3</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/4-18 NPTF x 1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>5404N</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Air-Way s84 only (double-pass 14 rows); PN carries cut length; C = body OD (no hex) | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>5404-N-04X3.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>5404-N-8-8 X 4</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="B27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>5404-N-8-8 X 4</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>Straight Pipe Nipple (round, NPTF x NPTF), 1/2-14 NPTF x 1/2-14 NPTF</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>5404N</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>1/2-14 NPTF</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>1/2-14 NPTF</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>Air-Way s84 only (double-pass 14 rows); PN carries cut length; C = body OD (no hex) | MODEL: round bar of Air-Way diameter C (no hex); male NPTF ends per ASME B1.20.3, threaded over L2 only (vanish threads NOT modelled - ASSUMPTION), the small step from the thread to the bar diameter is the difference between C and the pipe OD as printed; bore step at mid-length (ASSUMPTION)</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>5404-N-08X4.000</t>
         </is>
